--- a/output/北塩原村_前回計画の評価整理.xlsx
+++ b/output/北塩原村_前回計画の評価整理.xlsx
@@ -2663,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2721,6 +2721,21 @@
           <t>第７期障がい福祉計画・第３期障がい児福祉計画では、居宅介護、生活介護、就労継続支援、共同生活援助、計画相談支援等の主なサービスについては、概ね見込量に沿った利用となりました。また、地域生活支援拠点等の設置、コーディネーターの配置、就労定着支援等の成果目標については達成が見込まれます。
 一方、精神科病院からの地域移行、一般就労への移行、基幹相談支援センター、医療的ケア児支援の協議の場等については未達成又は検討中となっています。また、利用の実績が０であるサービスについても、今回のアンケート調査では移動、短期入所、緊急時の支援等の潜在的なニーズが確かめられているため、実績がないことをもってニーズがないとは評価しません。
 第８期計画では、過去の実績の延長だけで見込量を設定せず、ライフステージの変化を個別に把握するとともに、供給の制約を踏まえて必要な量と確保できる量を整理します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>委員会資料の第８期への反映</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>以上を踏まえ、第８期計画では次の三つを行います。
+第一に、見込量をお一人ずつの状況から積み上げます。18歳・卒業、40歳到達、65歳到達による介護保険への移行、精神科病院からの退院、親亡き後といったライフステージの変化を個別に把握します。そのための台帳の様式をお示ししますので、村において記入をお願いします。
+第二に、必要な量と確保できる量を分けて示します。事業所の受入れの余力、送迎、冬季の交通、人材の不足を確かめ、確保できない分は未充足量として記録します。見込量から引くと、不足が見えなくなります。
+第三に、達成の判定を数だけに置きません。設置した数や配置した人数ではなく、相談の件数、緊急時に受け入れた件数、地域生活へ移った方の数、調整が付かなかった件数で測ります。</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_前回計画の評価整理.xlsx
+++ b/output/北塩原村_前回計画の評価整理.xlsx
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>次回策定委員会に中間評価を出すため、次の指標の令和7年度実績又は令和8年度の最新値を確認したい。①特定健康診査の受診率②医療的ケア児の受入れ体制の実態③障がい者就労施設等からの物品調達件数（令和8年度）④障がい者に配慮した公共施設トイレの設置率⑤個別避難計画の策定件数（Ｍ-41で基準値の食い違いを照会中）。基準値（令和5年度）→現在値→令和11年度目標→進捗率、の形で委員会に示したい</t>
+          <t>次回策定委員会に中間評価を出すため、次の指標の令和7年度実績又は令和8年度の最新値を確認したい。①特定健康診査の受診率②医療的ケア児の受入れ体制の実態③障がい者就労施設等からの物品調達件数（令和8年度）④障がい者に配慮した公共施設トイレの設置率（第4次北塩原村障がい者計画は令和5年度の調査で村内の公共施設37施設のうち21施設・56.8％とし、「配慮した」の内容を車いす使用者が利用できる広さ、手すり、オストメイト対応の設備の設置等としています。同じ母数と同じ基準でお教えください）⑤個別避難計画の策定件数（Ｍ-41で基準値の食い違いを照会中）。基準値（令和5年度）→現在値→令和11年度目標→進捗率、の形で委員会に示したい</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
